--- a/static/Acc2.xlsx
+++ b/static/Acc2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lysenyj.nikolay\Desktop\для калькулятора\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lysenyj.nikolay\calc\acc_conf\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509D007B-0E4B-4CBC-8ABC-D2C3EBFD0964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B9D01E-9FC9-4612-B51F-30E2897913A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2BABEBC-3656-4A0D-978D-B963CC88D9B4}"/>
   </bookViews>
@@ -1114,7 +1114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1136,6 +1136,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1205,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1244,6 +1250,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5270,7 +5280,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -5293,7 +5303,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -5316,7 +5326,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -5342,7 +5352,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5370,27 +5380,31 @@
       </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:11" s="22" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="22" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="22">
+        <f>83+23</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -5413,7 +5427,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -5436,7 +5450,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -5456,82 +5470,94 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:11" s="22" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="22" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="K25" s="22">
+        <f>84+23</f>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="22" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="K26" s="22">
+        <f>85+23</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="22" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="22">
+        <f>85+23</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -5551,7 +5577,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -5574,7 +5600,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -5600,7 +5626,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -5626,7 +5652,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -5649,7 +5675,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -5672,7 +5698,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -5698,7 +5724,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -5723,8 +5749,12 @@
       <c r="I35" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <f>101-78</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -5746,8 +5776,12 @@
       <c r="I36" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <f>78+23</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -5770,7 +5804,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -5796,7 +5830,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -5824,7 +5858,7 @@
       </c>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -5844,7 +5878,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -5867,7 +5901,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -5893,7 +5927,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -5919,7 +5953,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -5939,7 +5973,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -5962,7 +5996,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -5988,7 +6022,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -6014,7 +6048,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -7549,7 +7583,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -7575,7 +7609,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -7603,102 +7637,118 @@
       </c>
       <c r="J114" s="2"/>
     </row>
-    <row r="115" spans="1:10" s="1" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
+    <row r="115" spans="1:11" s="22" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="F115" s="13">
-        <v>3</v>
-      </c>
-      <c r="G115" s="1" t="s">
+      <c r="F115" s="23">
+        <v>3</v>
+      </c>
+      <c r="G115" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="I115" s="1" t="s">
+      <c r="H115" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="I115" s="22" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+      <c r="K115" s="22">
+        <f>81+23</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F116" s="13">
-        <v>3</v>
-      </c>
-      <c r="G116" s="1" t="s">
+      <c r="F116" s="23">
+        <v>3</v>
+      </c>
+      <c r="G116" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="I116" s="1" t="s">
+      <c r="H116" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="I116" s="22" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
+      <c r="K116" s="22">
+        <f>79+23</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="13">
-        <v>3</v>
-      </c>
-      <c r="G117" s="1" t="s">
+      <c r="F117" s="23">
+        <v>3</v>
+      </c>
+      <c r="G117" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="H117" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="I117" s="1" t="s">
+      <c r="H117" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="I117" s="22" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+      <c r="K117" s="22">
+        <f>80+23</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F118" s="13">
-        <v>3</v>
-      </c>
-      <c r="G118" s="1" t="s">
+      <c r="F118" s="23">
+        <v>3</v>
+      </c>
+      <c r="G118" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="I118" s="1" t="s">
+      <c r="H118" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="I118" s="22" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K118" s="22">
+        <f>80+23</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -7718,7 +7768,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -7741,7 +7791,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -7767,7 +7817,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>7</v>
       </c>
@@ -7795,7 +7845,7 @@
       </c>
       <c r="J122" s="2"/>
     </row>
-    <row r="123" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -7818,7 +7868,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>0</v>
       </c>
@@ -7844,7 +7894,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>0</v>
       </c>
@@ -7870,7 +7920,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>7</v>
       </c>
@@ -7890,7 +7940,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="127" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>7</v>
       </c>
@@ -7913,7 +7963,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -8301,29 +8351,25 @@
         <v>257</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
+    <row r="144" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-      <c r="E144" s="1"/>
-      <c r="F144" s="9">
-        <v>3</v>
-      </c>
-      <c r="G144" t="s">
+      <c r="F144" s="23">
+        <v>3</v>
+      </c>
+      <c r="G144" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="H144" t="s">
-        <v>302</v>
-      </c>
-      <c r="I144" s="1" t="s">
+      <c r="H144" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="I144" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
@@ -8769,29 +8815,25 @@
         <v>257</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A164" s="1" t="s">
+    <row r="164" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-      <c r="E164" s="1"/>
-      <c r="F164" s="9">
-        <v>3</v>
-      </c>
-      <c r="G164" t="s">
+      <c r="F164" s="23">
+        <v>3</v>
+      </c>
+      <c r="G164" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="H164" t="s">
-        <v>302</v>
-      </c>
-      <c r="I164" s="1" t="s">
+      <c r="H164" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="I164" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="J164" s="1"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
